--- a/excel_files/MP3Tag_Mappings.xlsx
+++ b/excel_files/MP3Tag_Mappings.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\src\generated_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA0A163-3634-43FE-A376-CCB5E11800F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3816C6A-F2A6-4B56-9753-2041261563AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{734FDB5F-9A0D-4C22-83E5-5754F2D1B3BA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{734FDB5F-9A0D-4C22-83E5-5754F2D1B3BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sources" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="286">
   <si>
     <t>Name in Mp3tag</t>
   </si>
@@ -867,6 +868,84 @@
   </si>
   <si>
     <t>http://ffmpeg.org/pipermail/ffmpeg-user/attachments/20181208/87040191/attachment.obj dl and rename obj to xlsx</t>
+  </si>
+  <si>
+    <t>https://web.archive.org/web/20040401200215/reactor-core.org/ogg-tag-recommendations.html</t>
+  </si>
+  <si>
+    <t>Vorbis</t>
+  </si>
+  <si>
+    <t>MP3Tag</t>
+  </si>
+  <si>
+    <t>FFMPEG</t>
+  </si>
+  <si>
+    <t>fields of VorbisComments (used with FLAC) are not mapped internally by Mp3tag but are displayed with their actual name unless they use a user defined mapping</t>
+  </si>
+  <si>
+    <t>ALBUM</t>
+  </si>
+  <si>
+    <t>ALBUMARTIST</t>
+  </si>
+  <si>
+    <t>ARTIST</t>
+  </si>
+  <si>
+    <t>COMMENT</t>
+  </si>
+  <si>
+    <t>COMPOSER</t>
+  </si>
+  <si>
+    <t>CONDUCTOR</t>
+  </si>
+  <si>
+    <t>COPYRIGHT</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
+    <t>DISCNUMBER</t>
+  </si>
+  <si>
+    <t>GENRE</t>
+  </si>
+  <si>
+    <t>LYRICIST</t>
+  </si>
+  <si>
+    <t>TITLE</t>
+  </si>
+  <si>
+    <t>TRACKNUMBER</t>
+  </si>
+  <si>
+    <t>one of the 3 built-in technical MP3Tag to Vorbis mappings</t>
+  </si>
+  <si>
+    <t>ORGANIZATION</t>
+  </si>
+  <si>
+    <t>ACOUSTID_FINGERPRINT</t>
+  </si>
+  <si>
+    <t>ACOUSTID_ID</t>
+  </si>
+  <si>
+    <t>See MP3Tag YEAR</t>
+  </si>
+  <si>
+    <t>ISCR</t>
+  </si>
+  <si>
+    <t>??</t>
   </si>
 </sst>
 </file>
@@ -938,7 +1017,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -987,6 +1066,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1016,7 +1107,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -1069,10 +1160,20 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1388,16 +1489,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2156D25B-3C27-4FF6-8D3E-055BF1FDA5A8}">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="121.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.140625" customWidth="1"/>
+    <col min="7" max="7" width="174.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1414,10 +1516,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>6</v>
       </c>
@@ -1432,10 +1537,13 @@
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+      <c r="G2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>9</v>
       </c>
@@ -1449,11 +1557,12 @@
         <v>11</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1469,11 +1578,12 @@
       <c r="E4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F4" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -1489,11 +1599,10 @@
       <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F5" s="21"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -1509,11 +1618,12 @@
       <c r="E6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>24</v>
       </c>
@@ -1527,11 +1637,10 @@
         <v>26</v>
       </c>
       <c r="E7" s="12"/>
-      <c r="F7" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F7" s="22"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>246</v>
       </c>
@@ -1544,14 +1653,13 @@
       <c r="D8" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="F8" s="21" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="21"/>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>27</v>
       </c>
@@ -1567,9 +1675,12 @@
       <c r="E9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F9" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
@@ -1585,9 +1696,10 @@
       <c r="E10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F10" s="23"/>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>35</v>
       </c>
@@ -1603,9 +1715,10 @@
       <c r="E11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="23"/>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
@@ -1621,11 +1734,14 @@
       <c r="E12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>43</v>
       </c>
@@ -1641,11 +1757,12 @@
       <c r="E13" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="24"/>
+      <c r="G13" s="6" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>46</v>
       </c>
@@ -1661,9 +1778,12 @@
       <c r="E14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F14" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>50</v>
       </c>
@@ -1677,9 +1797,10 @@
         <v>52</v>
       </c>
       <c r="E15" s="12"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F15" s="22"/>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>53</v>
       </c>
@@ -1695,9 +1816,12 @@
       <c r="E16" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F16" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>57</v>
       </c>
@@ -1713,9 +1837,10 @@
       <c r="E17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="23"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>61</v>
       </c>
@@ -1731,9 +1856,12 @@
       <c r="E18" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F18" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>65</v>
       </c>
@@ -1745,9 +1873,12 @@
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="12"/>
-      <c r="F19" s="6"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F19" s="22"/>
+      <c r="G19" s="6" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>68</v>
       </c>
@@ -1758,10 +1889,13 @@
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>70</v>
       </c>
@@ -1777,9 +1911,12 @@
       <c r="E21" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F21" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>74</v>
       </c>
@@ -1795,9 +1932,10 @@
       <c r="E22" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F22" s="22"/>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>78</v>
       </c>
@@ -1813,9 +1951,10 @@
       <c r="E23" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F23" s="22"/>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>81</v>
       </c>
@@ -1827,9 +1966,10 @@
       <c r="E24" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F24" s="6"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F24" s="22"/>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
         <v>84</v>
       </c>
@@ -1841,9 +1981,10 @@
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="12"/>
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F25" s="22"/>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>86</v>
       </c>
@@ -1855,9 +1996,10 @@
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="12"/>
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F26" s="22"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>88</v>
       </c>
@@ -1873,9 +2015,12 @@
       <c r="E27" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F27" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>91</v>
       </c>
@@ -1887,9 +2032,10 @@
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="12"/>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F28" s="22"/>
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>93</v>
       </c>
@@ -1903,9 +2049,10 @@
       <c r="E29" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F29" s="22"/>
+      <c r="G29" s="6"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>96</v>
       </c>
@@ -1917,11 +2064,12 @@
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="12"/>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="22"/>
+      <c r="G30" s="6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>100</v>
       </c>
@@ -1935,9 +2083,12 @@
       <c r="E31" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F31" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="G31" s="6"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>103</v>
       </c>
@@ -1951,9 +2102,10 @@
       <c r="E32" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F32" s="22"/>
+      <c r="G32" s="6"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>106</v>
       </c>
@@ -1965,9 +2117,10 @@
       </c>
       <c r="D33" s="11"/>
       <c r="E33" s="12"/>
-      <c r="F33" s="6"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F33" s="22"/>
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>108</v>
       </c>
@@ -1979,9 +2132,12 @@
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="12"/>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F34" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>110</v>
       </c>
@@ -1997,9 +2153,10 @@
       <c r="E35" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="F35" s="6"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F35" s="22"/>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
         <v>112</v>
       </c>
@@ -2011,9 +2168,10 @@
       </c>
       <c r="D36" s="11"/>
       <c r="E36" s="12"/>
-      <c r="F36" s="6"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F36" s="22"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
         <v>114</v>
       </c>
@@ -2027,11 +2185,12 @@
       <c r="E37" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="22"/>
+      <c r="G37" s="6" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>117</v>
       </c>
@@ -2045,9 +2204,10 @@
         <v>119</v>
       </c>
       <c r="E38" s="12"/>
-      <c r="F38" s="6"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F38" s="22"/>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
         <v>120</v>
       </c>
@@ -2061,9 +2221,10 @@
         <v>122</v>
       </c>
       <c r="E39" s="12"/>
-      <c r="F39" s="6"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F39" s="22"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
         <v>123</v>
       </c>
@@ -2077,9 +2238,10 @@
         <v>124</v>
       </c>
       <c r="E40" s="12"/>
-      <c r="F40" s="6"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F40" s="22"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
         <v>125</v>
       </c>
@@ -2089,11 +2251,12 @@
       </c>
       <c r="D41" s="11"/>
       <c r="E41" s="12"/>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="22"/>
+      <c r="G41" s="6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
         <v>127</v>
       </c>
@@ -2103,9 +2266,10 @@
         <v>128</v>
       </c>
       <c r="E42" s="12"/>
-      <c r="F42" s="6"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F42" s="22"/>
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
         <v>129</v>
       </c>
@@ -2117,9 +2281,10 @@
       </c>
       <c r="D43" s="11"/>
       <c r="E43" s="12"/>
-      <c r="F43" s="6"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F43" s="22"/>
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>131</v>
       </c>
@@ -2131,9 +2296,10 @@
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="12"/>
-      <c r="F44" s="6"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F44" s="22"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>133</v>
       </c>
@@ -2147,9 +2313,10 @@
       <c r="E45" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F45" s="6"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F45" s="22"/>
+      <c r="G45" s="6"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>136</v>
       </c>
@@ -2163,9 +2330,10 @@
       <c r="E46" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F46" s="6"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F46" s="22"/>
+      <c r="G46" s="6"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
         <v>139</v>
       </c>
@@ -2179,9 +2347,10 @@
       <c r="E47" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F47" s="6"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F47" s="22"/>
+      <c r="G47" s="6"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>142</v>
       </c>
@@ -2195,9 +2364,10 @@
       <c r="E48" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="F48" s="6"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F48" s="22"/>
+      <c r="G48" s="6"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
         <v>145</v>
       </c>
@@ -2211,9 +2381,10 @@
       <c r="E49" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F49" s="6"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F49" s="22"/>
+      <c r="G49" s="6"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
         <v>149</v>
       </c>
@@ -2227,11 +2398,12 @@
         <v>151</v>
       </c>
       <c r="E50" s="12"/>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="22"/>
+      <c r="G50" s="6" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
         <v>153</v>
       </c>
@@ -2245,9 +2417,10 @@
         <v>155</v>
       </c>
       <c r="E51" s="12"/>
-      <c r="F51" s="6"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F51" s="22"/>
+      <c r="G51" s="6"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="15" t="s">
         <v>156</v>
       </c>
@@ -2261,9 +2434,10 @@
         <v>158</v>
       </c>
       <c r="E52" s="12"/>
-      <c r="F52" s="6"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F52" s="22"/>
+      <c r="G52" s="6"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
         <v>159</v>
       </c>
@@ -2277,9 +2451,10 @@
         <v>161</v>
       </c>
       <c r="E53" s="12"/>
-      <c r="F53" s="6"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F53" s="22"/>
+      <c r="G53" s="6"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="15" t="s">
         <v>162</v>
       </c>
@@ -2293,9 +2468,10 @@
         <v>164</v>
       </c>
       <c r="E54" s="12"/>
-      <c r="F54" s="6"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F54" s="22"/>
+      <c r="G54" s="6"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="15" t="s">
         <v>165</v>
       </c>
@@ -2309,9 +2485,10 @@
         <v>167</v>
       </c>
       <c r="E55" s="12"/>
-      <c r="F55" s="6"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F55" s="22"/>
+      <c r="G55" s="6"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="15" t="s">
         <v>168</v>
       </c>
@@ -2323,11 +2500,12 @@
       </c>
       <c r="D56" s="11"/>
       <c r="E56" s="12"/>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="22"/>
+      <c r="G56" s="6" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>170</v>
       </c>
@@ -2343,9 +2521,14 @@
       <c r="E57" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F57" s="6"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F57" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>174</v>
       </c>
@@ -2355,17 +2538,18 @@
       <c r="C58" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D58" s="20" t="s">
+      <c r="D58" s="6" t="s">
         <v>252</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="22"/>
+      <c r="G58" s="6" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
         <v>176</v>
       </c>
@@ -2377,9 +2561,10 @@
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="12"/>
-      <c r="F59" s="6"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F59" s="22"/>
+      <c r="G59" s="6"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
         <v>178</v>
       </c>
@@ -2389,9 +2574,10 @@
       </c>
       <c r="D60" s="11"/>
       <c r="E60" s="12"/>
-      <c r="F60" s="6"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F60" s="22"/>
+      <c r="G60" s="6"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>180</v>
       </c>
@@ -2405,9 +2591,10 @@
       <c r="E61" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="F61" s="6"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F61" s="22"/>
+      <c r="G61" s="6"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
         <v>183</v>
       </c>
@@ -2417,9 +2604,10 @@
       </c>
       <c r="D62" s="11"/>
       <c r="E62" s="12"/>
-      <c r="F62" s="6"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F62" s="22"/>
+      <c r="G62" s="6"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>185</v>
       </c>
@@ -2435,9 +2623,12 @@
       <c r="E63" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="F63" s="6"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F63" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G63" s="6"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>189</v>
       </c>
@@ -2453,9 +2644,10 @@
       <c r="E64" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="F64" s="6"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F64" s="22"/>
+      <c r="G64" s="6"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>193</v>
       </c>
@@ -2471,9 +2663,14 @@
       <c r="E65" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="F65" s="6"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F65" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="15" t="s">
         <v>197</v>
       </c>
@@ -2485,9 +2682,10 @@
       </c>
       <c r="D66" s="11"/>
       <c r="E66" s="12"/>
-      <c r="F66" s="6"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F66" s="22"/>
+      <c r="G66" s="6"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>199</v>
       </c>
@@ -2503,11 +2701,12 @@
       <c r="E67" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="F67" s="6" t="s">
+      <c r="F67" s="22"/>
+      <c r="G67" s="6" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
         <v>204</v>
       </c>
@@ -2519,9 +2718,10 @@
       </c>
       <c r="D68" s="11"/>
       <c r="E68" s="12"/>
-      <c r="F68" s="6"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F68" s="22"/>
+      <c r="G68" s="6"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
         <v>206</v>
       </c>
@@ -2535,9 +2735,10 @@
       <c r="E69" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="F69" s="6"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F69" s="22"/>
+      <c r="G69" s="6"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
         <v>209</v>
       </c>
@@ -2551,9 +2752,10 @@
       <c r="E70" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F70" s="6"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F70" s="22"/>
+      <c r="G70" s="6"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="15" t="s">
         <v>212</v>
       </c>
@@ -2567,9 +2769,10 @@
       <c r="E71" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F71" s="6"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F71" s="22"/>
+      <c r="G71" s="6"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
         <v>215</v>
       </c>
@@ -2583,9 +2786,10 @@
       <c r="E72" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="F72" s="6"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F72" s="22"/>
+      <c r="G72" s="6"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="15" t="s">
         <v>218</v>
       </c>
@@ -2599,9 +2803,10 @@
       <c r="E73" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F73" s="6"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F73" s="22"/>
+      <c r="G73" s="6"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
         <v>221</v>
       </c>
@@ -2613,9 +2818,10 @@
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="12"/>
-      <c r="F74" s="6"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F74" s="22"/>
+      <c r="G74" s="6"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
         <v>223</v>
       </c>
@@ -2627,9 +2833,10 @@
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="12"/>
-      <c r="F75" s="6"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F75" s="22"/>
+      <c r="G75" s="6"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="15" t="s">
         <v>225</v>
       </c>
@@ -2641,9 +2848,10 @@
       </c>
       <c r="D76" s="11"/>
       <c r="E76" s="12"/>
-      <c r="F76" s="6"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F76" s="22"/>
+      <c r="G76" s="6"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>227</v>
       </c>
@@ -2659,9 +2867,14 @@
       <c r="E77" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="F77" s="6"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F77" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>232</v>
       </c>
@@ -2677,12 +2890,13 @@
       <c r="E78" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="F78" s="6"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F78" s="4"/>
+      <c r="G78" s="6"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
     </row>
-    <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
     </row>
   </sheetData>
@@ -2763,7 +2977,77 @@
     <hyperlink ref="A76" r:id="rId74" location="wwwradiopage" display="https://docs.mp3tag.de/mapping-table/ - wwwradiopage" xr:uid="{1F4697C3-8002-4737-BEA5-61C083D6DFA7}"/>
     <hyperlink ref="A77" r:id="rId75" location="year" display="https://docs.mp3tag.de/mapping-table/ - year" xr:uid="{EFD75774-1055-4393-9EE4-AE9C5D250623}"/>
     <hyperlink ref="A78" r:id="rId76" location="other-fields" display="https://docs.mp3tag.de/mapping-table/ - other-fields" xr:uid="{1BFE8748-7918-4A56-B501-9123FF2BC9AD}"/>
-    <hyperlink ref="F8" r:id="rId77" xr:uid="{F107A0CE-F201-4458-AC66-9DF6DC035E71}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F2BAA1-CDAD-4B28-835C-1772E0AEC7C2}">
+  <dimension ref="A2:B9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="108" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="20" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="20" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="20" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="20" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>285</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{9362381A-2C5A-42EE-BDAD-EB8DA6D1370F}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{C1EBA628-3A0E-4F18-8053-E4410F7D6456}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{5A1F4A2B-5C02-42C5-8E6F-A18B7A7B7246}"/>
+    <hyperlink ref="B4" r:id="rId4" xr:uid="{A47D33D1-1392-4703-B4D4-38B94FE152EB}"/>
+    <hyperlink ref="B5" r:id="rId5" xr:uid="{1C64057E-4802-42DD-A899-0EA464FDD6C1}"/>
+    <hyperlink ref="B6" r:id="rId6" xr:uid="{7FCF62A8-20C3-4867-B2FE-AA7205E5D62B}"/>
+    <hyperlink ref="B7" r:id="rId7" xr:uid="{7080B8CF-6DB8-4C6C-AF74-0CF2B7B71FCD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
